--- a/data/pinjaman_cicilan.xlsx
+++ b/data/pinjaman_cicilan.xlsx
@@ -417,21 +417,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="49" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
@@ -508,6 +508,204 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>afe9b9f3-918c-4975-b178-9f2794b2b1f2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>818c78aa-207f-4391-baa3-84113c97f8c7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>05e37a03-9165-48a5-961e-8c5c3e18a50c</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>83e839bc-9a6d-4c81-9c34-230b337d794d</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4666666.67</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Pengajuan pembayaran via Indomaret</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Indomaret</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6044ebf4-14d4-419c-98fe-488820d67b32</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>83e839bc-9a6d-4c81-9c34-230b337d794d</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5665000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/pinjaman_cicilan.xlsx
+++ b/data/pinjaman_cicilan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -427,11 +427,11 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="49" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
@@ -706,6 +706,666 @@
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>299206df-6905-4772-90e3-55514910a7bd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>f367c691-a2f0-4d53-9ab4-5245da1d2c79</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bcc5d787-da35-4a0f-82ad-5bece6057d2d</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>a1e62512-e12c-4c9e-8c6e-46e66d6defd9</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5c3b5166-9782-461a-871a-84e26390578d</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cbd22f05-132e-4ddf-8ba5-ca7e306436a2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>45c6ff6d-07cb-444c-b247-9eddc86f0619</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bb49d551-d681-4e18-8368-9f52e6124432</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7a07b48a-e3f3-471f-8544-bfc75d4fee8a</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6bdd5734-e70e-4361-921c-df82ffc9649d</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>262c015e-cec3-4f84-9472-c00666df98b3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>192000000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1efab583-80c0-42e9-94c0-f48e25473f5e</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AGT-020</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Siti Aulia</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>384000000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/pinjaman_cicilan.xlsx
+++ b/data/pinjaman_cicilan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:S60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -433,7 +433,12 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,39 +512,64 @@
           <t>detail_pembayaran</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>status_transaksi</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>va_number</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>idempotency_key</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>periode_tagihan</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>expires_at</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>afe9b9f3-918c-4975-b178-9f2794b2b1f2</t>
+          <t>381fb919-2d28-4b45-a14e-58f12ec22872</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>818c78aa-207f-4391-baa3-84113c97f8c7</t>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3000000</v>
+        <v>545000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -549,7 +579,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -573,49 +603,58 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05e37a03-9165-48a5-961e-8c5c3e18a50c</t>
+          <t>92df500e-7d3b-4587-8545-9bec4d9a5f64</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83e839bc-9a6d-4c81-9c34-230b337d794d</t>
+          <t>7aafe11b-5228-484a-9fe8-3b29d45a6677</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4666666.67</v>
+        <v>3000000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Disetujui</t>
+          <t>Gagal Bayar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -625,63 +664,72 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Pengajuan pembayaran via Indomaret</t>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Indomaret</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6044ebf4-14d4-419c-98fe-488820d67b32</t>
+          <t>dff9dac0-0310-4b0c-a92a-70ce2db2cc0d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>83e839bc-9a6d-4c81-9c34-230b337d794d</t>
+          <t>7aafe11b-5228-484a-9fe8-3b29d45a6677</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5665000</v>
+        <v>6000000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Disetujui</t>
+          <t>Gagal Bayar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -696,7 +744,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -705,49 +753,58 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>299206df-6905-4772-90e3-55514910a7bd</t>
+          <t>d8287785-a35f-4a9f-bfa8-93516c788c92</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>f367c691-a2f0-4d53-9ab4-5245da1d2c79</t>
+          <t>7aafe11b-5228-484a-9fe8-3b29d45a6677</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3000000</v>
+        <v>12000000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Disetujui</t>
+          <t>Gagal Bayar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -762,7 +819,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -771,49 +828,58 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bcc5d787-da35-4a0f-82ad-5bece6057d2d</t>
+          <t>79f5475c-ddcb-4b83-8093-e942c4b522e2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>a1e62512-e12c-4c9e-8c6e-46e66d6defd9</t>
+          <t>7aafe11b-5228-484a-9fe8-3b29d45a6677</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3000000</v>
+        <v>24000000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Disetujui</t>
+          <t>Gagal Bayar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -828,7 +894,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -837,39 +903,48 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5c3b5166-9782-461a-871a-84e26390578d</t>
+          <t>9b58ca44-55bf-42c8-a951-feccfbf60a89</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+          <t>7aafe11b-5228-484a-9fe8-3b29d45a6677</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3000000</v>
+        <v>48000000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -879,7 +954,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -903,49 +978,58 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cbd22f05-132e-4ddf-8ba5-ca7e306436a2</t>
+          <t>00a8a106-92ca-4b59-94a5-5b06d4140be4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+          <t>7aafe11b-5228-484a-9fe8-3b29d45a6677</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6000000</v>
+        <v>96000000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Gagal Bayar</t>
+          <t>Disetujui</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -960,7 +1044,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -969,39 +1053,48 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>45c6ff6d-07cb-444c-b247-9eddc86f0619</t>
+          <t>cefe2fce-69c4-468f-bd0a-9fed6479815a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>12000000</v>
+        <v>545000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1011,7 +1104,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1035,49 +1128,58 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bb49d551-d681-4e18-8368-9f52e6124432</t>
+          <t>eed0981c-3fb4-4288-9b71-e1af2f342821</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>24000000</v>
+        <v>545000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Gagal Bayar</t>
+          <t>Disetujui</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1092,7 +1194,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1101,49 +1203,58 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7a07b48a-e3f3-471f-8544-bfc75d4fee8a</t>
+          <t>718338bf-de38-46de-a872-37dfaea161c6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>48000000</v>
+        <v>545000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Gagal Bayar</t>
+          <t>Disetujui</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1158,7 +1269,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1167,39 +1278,48 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6bdd5734-e70e-4361-921c-df82ffc9649d</t>
+          <t>f492b1f4-b9ae-4184-ac2f-a631f6475f04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>96000000</v>
+        <v>545000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1209,7 +1329,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1233,39 +1353,48 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>262c015e-cec3-4f84-9472-c00666df98b3</t>
+          <t>f2c93fd8-feac-4b06-a816-84f93974c00d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>192000000</v>
+        <v>545000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1275,7 +1404,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1299,39 +1428,48 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1efab583-80c0-42e9-94c0-f48e25473f5e</t>
+          <t>ea03d04e-361d-4c8b-9f84-40177b381c9d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dd1ea271-cff9-4bf8-bc9b-c33bab1fc85a</t>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8e996a5b-71c2-4eb3-9545-91bd35986c46</t>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AGT-020</t>
+          <t>AGT-065</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Siti Aulia</t>
+          <t>Boseng</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>384000000</v>
+        <v>545000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1341,7 +1479,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1365,6 +1503,3477 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8cde0c4a-c0a2-420a-9261-41bb9e5ba38a</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>545000</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6f8806fa-373d-40e7-b8fc-210b69aac1e4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>545000</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ae9039c7-a68c-4f9f-b488-80b04c8d60f0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>545000</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>a3395a38-8ccf-4b6d-97b4-ad8565ee306d</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>545000</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>f4bc589f-37e5-4984-860c-ade09fc290a8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>739be525-a36b-496b-9d13-8415f2f8a211</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>275000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ab852625-ae8e-4ded-999a-ad709d12d55d</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>345000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>714ac1b3-8c4b-45ff-87db-35297355f19c</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>345000</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>11587cc2-d362-40e3-acb4-701658fcd6a4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>345000</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>a337862b-cb6b-417a-bb38-ad91e7e66d93</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>345000</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3761cc00-1814-4171-b769-552131d93891</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>345000</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>196d68f9-d9de-4ab8-b67e-102d67a04e3c</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>345000</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>a85e84ac-2451-4964-bf00-6eb005a20aeb</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>345000</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>33d917d5-c411-44a8-a5db-9899ffabc282</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>345000</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ef5145ac-4793-4086-ac18-8437226926ac</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>345000</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2dc4d008-5f91-4ed5-805c-d1311f7243b1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>345000</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0c875539-fed1-4aab-9e5b-d02b6c1c82ef</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7f58a662-a9dd-45db-b0fb-0a4973fd7848</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>240000</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3d5fdf72-d2e3-46d7-8b6f-ca1a3e2f9733</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>9d599acf-b867-4d42-82f9-7aae80d2c39e</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>82df5e77-15f2-4cb2-ba21-8c9c3fd8eb78</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cffa7ec4-3cba-4480-a338-b59973736be1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5c7e9958-c881-4a30-a12b-c195a7282d33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>783eaa56-8743-44da-9471-cc78ca371b92</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>096fae0a-f6fe-44b6-850a-e95b8fadde29</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>282aac7b-a484-41e6-8af7-6a134def1930</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>766d65ba-fd0f-466f-9843-7fc81cd634db</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ee54a9d5-16fc-4d13-8a4f-78b51abeeed5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>c1cecc30-29c9-45e8-a29e-60d9f5ba1d54</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>bb9f8966-3cc5-486d-a66a-8696a323aaaa</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0942eb18-9480-4758-a7a5-952bf5be3a0a</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>76c027b4-1bc5-4acc-b9b4-32e916cb9667</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>e2619ed0-2f5c-4c64-90c7-72e78416915d</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>21be77ae-a9cc-46e3-a2b6-8ccd610f5fd2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>a8804e4e-300b-4343-b611-4c03dcb94d68</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>58632868-72f9-495d-b15d-f7830a19f0b1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>7172cdc0-f4aa-425e-8f5d-5e660dc93e83</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>68ef4180-98d3-420c-9a23-a869a22eea9b</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3444bc24-d7e7-4939-b1cc-6397e0f58bcb</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>3222222.19</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>8b47fa6c-48eb-4f4a-86f0-438d5d4a7b4f</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ff92e6e6-3f46-42f6-995a-3dab9f9ab335</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>777777.77</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7d8ba2c1-e9a8-4fa2-a34e-1d703d05e5ac</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>67c0f79e-475d-492b-86aa-816e56e01c15</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>8440349d-5597-4703-b783-18d939de2451</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>7e79f8cd-8b23-476c-b9ca-a701a587ab48</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4d4e468b-1d5d-4dac-be0e-73886fcc6328</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Pengajuan pembayaran via Indomaret</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Indomaret</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>29fa391c-a5a2-42ae-b787-f35382b765bd</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>6990664e-e01f-43aa-ad8a-cc0d8c1ff238</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2638888.86</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>a4ed810c-f883-4f32-af38-30ac82041d1e</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>6990664e-e01f-43aa-ad8a-cc0d8c1ff238</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>88cc9888-05f9-4fc2-8865-c4942542b6ba</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AGT-065</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>2638888.86</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>966c2c8f-d08b-4508-a2d0-6e6ceba274ec</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>756d8650-36a6-4ca8-ad5b-9b282381d4fc</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Septiawan</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Menunggu</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>septiawan</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Pengajuan pembayaran via Transfer Bank — VA: 8800111888023165910 — QRIS-&gt;DANA 0881023452481 | REF ee8f7075-b | Nominal Rp 25.000.000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Transfer Bank</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>QRIS-&gt;DANA 0881023452481 | REF ee8f7075-b | Nominal Rp 25.000.000</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Menunggu Verifikasi</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>8.800111888023166e+18</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>ee8f7075-b565-4c35-84d0-7fb11bc88f80-1776938345037-o3bw3y7e</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2026-04-24 16:59:10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pinjaman_cicilan.xlsx
+++ b/data/pinjaman_cicilan.xlsx
@@ -434,7 +434,7 @@
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
     <col width="50" customWidth="1" min="17" max="17"/>
     <col width="17" customWidth="1" min="18" max="18"/>
@@ -4924,11 +4924,19 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Menunggu</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>Ditolak</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>system-expired</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>septiawan</t>
@@ -4951,7 +4959,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Menunggu Verifikasi</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">

--- a/data/pinjaman_cicilan.xlsx
+++ b/data/pinjaman_cicilan.xlsx
@@ -541,12 +541,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dd1ba262-5253-41ab-8b87-686a7323077d</t>
+          <t>800093f1-7908-4f4b-9f7d-4ac95ba424a9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9d80ef55-4a26-4154-bb6a-8e404784f616</t>
+          <t>ada754c8-4996-40de-9a0e-1ca4126e223b</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -604,7 +604,7 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>

--- a/data/pinjaman_cicilan.xlsx
+++ b/data/pinjaman_cicilan.xlsx
@@ -417,21 +417,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
@@ -609,6 +609,606 @@
       </c>
       <c r="S2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>e25d452a-319b-4f2e-a4c1-00934fd0fa38</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>902d0cdf-bfe5-4885-b08c-a305f59e4908</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>70d21614-df6f-4410-b9bd-e7e8fa8c5cad</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>701bedac-2920-4c8d-8acc-3bb40e64976d</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>f0086da4-2c5b-4b72-8139-5fbab3072507</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>778dd6b6-a4fa-4ce2-9811-9425df5f23f1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>23da7445-7a7c-4c8d-84ef-70afb3534567</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6ea93e4a-510f-4329-af28-2d68d25764f4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/pinjaman_cicilan.xlsx
+++ b/data/pinjaman_cicilan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1209,6 +1209,456 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4e8a6549-2176-4b72-b77d-6ea0f61bfbaf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cabd1822-9043-4c67-bc94-aef576aa6fcd</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ae9c9727-5e22-4566-9cda-ce59c705b08f</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>07cbc96c-199d-4bfc-8dfc-5055bb49f375</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>238285.71</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8ed57465-8cbb-4279-9df0-cabeb2e8540d</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>c012c367-b8fe-4964-b89e-0f0478e3d31a</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1045000</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>c0a9a922-8332-4b84-83a0-40705d4459f5</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>c012c367-b8fe-4964-b89e-0f0478e3d31a</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1045000</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>super_admin</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/pinjaman_cicilan.xlsx
+++ b/data/pinjaman_cicilan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -430,7 +430,7 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
@@ -1659,6 +1659,81 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bc5eb8c9-2dea-490e-8252-2c8d1bdb05fb</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>d453c433-d6bc-4c58-b811-5d54b7331a90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3991250</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>admin_koperasi</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>admin_koperasi</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/pinjaman_cicilan.xlsx
+++ b/data/pinjaman_cicilan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -425,7 +425,7 @@
     <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -1734,6 +1734,949 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>e0865e35-ab87-4239-be56-a5fc0a85c0ad</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>c012c367-b8fe-4964-b89e-0f0478e3d31a</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>70529c75-ae75-4e21-978a-a1430d0f85f0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>c012c367-b8fe-4964-b89e-0f0478e3d31a</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>82ba18dc-eabe-4f7e-b5e6-61f84c96515c</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>c012c367-b8fe-4964-b89e-0f0478e3d31a</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ae8ae1ad-c627-447c-bbb8-1a3edb8a27e7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>c012c367-b8fe-4964-b89e-0f0478e3d31a</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1df2757b-f56f-4fb4-94b8-86b03683e722</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>b59dca00-0471-448f-a0f6-b954f8a658dd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>419827.59</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0e9bd669-2fb2-4ddf-8608-d9795a440a59</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>b59dca00-0471-448f-a0f6-b954f8a658dd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>419827.59</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4c56bbb4-c8ae-44c0-a85e-0792b15a13ce</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>b59dca00-0471-448f-a0f6-b954f8a658dd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>419827.59</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>558a6890-925d-4e13-ace2-85c5188eb8a3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>b59dca00-0471-448f-a0f6-b954f8a658dd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>9580172.41</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Pelunasan pinjaman melalui admin (bayar lunas)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Pelunasan</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>216273e7-6e25-43f2-87a9-f09110567d25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>8ab14b82-442f-4b20-9f3d-245c2c745bea</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>408333.33</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1fd3c153-15d8-47cc-a0af-12a26bb17689</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>8ab14b82-442f-4b20-9f3d-245c2c745bea</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>408333.33</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>8d196901-eb39-4049-8af5-76b4299e1f86</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>8ab14b82-442f-4b20-9f3d-245c2c745bea</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>408333.33</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cadb45b4-d07a-4102-afc8-c14bf2265dca</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>8ab14b82-442f-4b20-9f3d-245c2c745bea</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>408333.33</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Pembayaran cicilan melalui admin (kas koperasi)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Berhasil</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0a719617-43e0-416b-8a50-d2e8e524858c</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>8ab14b82-442f-4b20-9f3d-245c2c745bea</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>408333.33</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>superadmin</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Gagal bayar cicilan (terlambat / tidak tepat waktu)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Draft</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
